--- a/tests/reports/appium_android_300_report.xlsx
+++ b/tests/reports/appium_android_300_report.xlsx
@@ -219,19 +219,19 @@
     <t>MOB-006</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 1)</t>
+    <t>Native UI sync (Variant 1)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Initialize Appium Android environment.
 2. Navigate to App Lifecycle &amp; Native.
-3. Perform 'Capacitor webview sync'.
+3. Perform 'Native UI sync'.
 4. Assert output and state.</t>
   </si>
   <si>
-    <t>System should process 'Capacitor webview sync' cleanly without failure.</t>
-  </si>
-  <si>
-    <t>PASS — Appium Android verified 'Capacitor webview sync' with expected output.</t>
+    <t>System should process 'Native UI sync' cleanly without failure.</t>
+  </si>
+  <si>
+    <t>PASS — Appium Android verified 'Native UI sync' with expected output.</t>
   </si>
   <si>
     <t>MOB-007</t>
@@ -621,7 +621,7 @@
     <t>MOB-031</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 4)</t>
+    <t>Native UI sync (Variant 4)</t>
   </si>
   <si>
     <t>MOB-032</t>
@@ -771,7 +771,7 @@
     <t>MOB-056</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 6)</t>
+    <t>Native UI sync (Variant 6)</t>
   </si>
   <si>
     <t>MOB-057</t>
@@ -921,7 +921,7 @@
     <t>MOB-081</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 9)</t>
+    <t>Native UI sync (Variant 9)</t>
   </si>
   <si>
     <t>MOB-082</t>
@@ -1071,7 +1071,7 @@
     <t>MOB-106</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 11)</t>
+    <t>Native UI sync (Variant 11)</t>
   </si>
   <si>
     <t>MOB-107</t>
@@ -1221,7 +1221,7 @@
     <t>MOB-131</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 14)</t>
+    <t>Native UI sync (Variant 14)</t>
   </si>
   <si>
     <t>MOB-132</t>
@@ -1371,7 +1371,7 @@
     <t>MOB-156</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 16)</t>
+    <t>Native UI sync (Variant 16)</t>
   </si>
   <si>
     <t>MOB-157</t>
@@ -1521,7 +1521,7 @@
     <t>MOB-181</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 19)</t>
+    <t>Native UI sync (Variant 19)</t>
   </si>
   <si>
     <t>MOB-182</t>
@@ -1671,7 +1671,7 @@
     <t>MOB-206</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 21)</t>
+    <t>Native UI sync (Variant 21)</t>
   </si>
   <si>
     <t>MOB-207</t>
@@ -1821,7 +1821,7 @@
     <t>MOB-231</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 24)</t>
+    <t>Native UI sync (Variant 24)</t>
   </si>
   <si>
     <t>MOB-232</t>
@@ -1971,7 +1971,7 @@
     <t>MOB-256</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 26)</t>
+    <t>Native UI sync (Variant 26)</t>
   </si>
   <si>
     <t>MOB-257</t>
@@ -2121,7 +2121,7 @@
     <t>MOB-281</t>
   </si>
   <si>
-    <t>Capacitor webview sync (Variant 29)</t>
+    <t>Native UI sync (Variant 29)</t>
   </si>
   <si>
     <t>MOB-282</t>
@@ -2921,7 +2921,7 @@
         <v>35</v>
       </c>
       <c r="J2" s="6">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>36</v>
@@ -2959,7 +2959,7 @@
         <v>43</v>
       </c>
       <c r="J3" s="8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>36</v>
@@ -2997,7 +2997,7 @@
         <v>49</v>
       </c>
       <c r="J4" s="6">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>36</v>
@@ -3035,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="J5" s="8">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>36</v>
@@ -3073,7 +3073,7 @@
         <v>35</v>
       </c>
       <c r="J6" s="6">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>36</v>
@@ -3111,7 +3111,7 @@
         <v>43</v>
       </c>
       <c r="J7" s="8">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>36</v>
@@ -3149,7 +3149,7 @@
         <v>49</v>
       </c>
       <c r="J8" s="6">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>36</v>
@@ -3187,7 +3187,7 @@
         <v>55</v>
       </c>
       <c r="J9" s="8">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>36</v>
@@ -3225,7 +3225,7 @@
         <v>35</v>
       </c>
       <c r="J10" s="6">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>36</v>
@@ -3263,7 +3263,7 @@
         <v>43</v>
       </c>
       <c r="J11" s="8">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>36</v>
@@ -3301,7 +3301,7 @@
         <v>49</v>
       </c>
       <c r="J12" s="6">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>36</v>
@@ -3339,7 +3339,7 @@
         <v>55</v>
       </c>
       <c r="J13" s="8">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>36</v>
@@ -3377,7 +3377,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="6">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>36</v>
@@ -3415,7 +3415,7 @@
         <v>43</v>
       </c>
       <c r="J15" s="8">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>49</v>
       </c>
       <c r="J16" s="6">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>36</v>
@@ -3491,7 +3491,7 @@
         <v>55</v>
       </c>
       <c r="J17" s="8">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>36</v>
@@ -3567,7 +3567,7 @@
         <v>43</v>
       </c>
       <c r="J19" s="8">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>36</v>
@@ -3605,7 +3605,7 @@
         <v>49</v>
       </c>
       <c r="J20" s="6">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>36</v>
@@ -3643,7 +3643,7 @@
         <v>55</v>
       </c>
       <c r="J21" s="8">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>36</v>
@@ -3681,7 +3681,7 @@
         <v>35</v>
       </c>
       <c r="J22" s="6">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>36</v>
@@ -3719,7 +3719,7 @@
         <v>43</v>
       </c>
       <c r="J23" s="8">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>36</v>
@@ -3757,7 +3757,7 @@
         <v>49</v>
       </c>
       <c r="J24" s="6">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>36</v>
@@ -3795,7 +3795,7 @@
         <v>55</v>
       </c>
       <c r="J25" s="8">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>36</v>
@@ -3833,7 +3833,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="6">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>36</v>
@@ -3871,7 +3871,7 @@
         <v>43</v>
       </c>
       <c r="J27" s="8">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>36</v>
@@ -3909,7 +3909,7 @@
         <v>49</v>
       </c>
       <c r="J28" s="6">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>36</v>
@@ -3947,7 +3947,7 @@
         <v>55</v>
       </c>
       <c r="J29" s="8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>36</v>
@@ -3985,7 +3985,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="6">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>36</v>
@@ -4023,7 +4023,7 @@
         <v>43</v>
       </c>
       <c r="J31" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>36</v>
@@ -4061,7 +4061,7 @@
         <v>49</v>
       </c>
       <c r="J32" s="6">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>36</v>
@@ -4099,7 +4099,7 @@
         <v>55</v>
       </c>
       <c r="J33" s="8">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>36</v>
@@ -4137,7 +4137,7 @@
         <v>35</v>
       </c>
       <c r="J34" s="6">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>36</v>
@@ -4175,7 +4175,7 @@
         <v>43</v>
       </c>
       <c r="J35" s="8">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>36</v>
@@ -4213,7 +4213,7 @@
         <v>49</v>
       </c>
       <c r="J36" s="6">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>36</v>
@@ -4251,7 +4251,7 @@
         <v>55</v>
       </c>
       <c r="J37" s="8">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>36</v>
@@ -4289,7 +4289,7 @@
         <v>35</v>
       </c>
       <c r="J38" s="6">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>36</v>
@@ -4327,7 +4327,7 @@
         <v>43</v>
       </c>
       <c r="J39" s="8">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>36</v>
@@ -4365,7 +4365,7 @@
         <v>49</v>
       </c>
       <c r="J40" s="6">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>36</v>
@@ -4403,7 +4403,7 @@
         <v>55</v>
       </c>
       <c r="J41" s="8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>36</v>
@@ -4441,7 +4441,7 @@
         <v>35</v>
       </c>
       <c r="J42" s="6">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>36</v>
@@ -4479,7 +4479,7 @@
         <v>43</v>
       </c>
       <c r="J43" s="8">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>36</v>
@@ -4517,7 +4517,7 @@
         <v>49</v>
       </c>
       <c r="J44" s="6">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>36</v>
@@ -4555,7 +4555,7 @@
         <v>55</v>
       </c>
       <c r="J45" s="8">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>36</v>
@@ -4593,7 +4593,7 @@
         <v>35</v>
       </c>
       <c r="J46" s="6">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>36</v>
@@ -4631,7 +4631,7 @@
         <v>43</v>
       </c>
       <c r="J47" s="8">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>36</v>
@@ -4669,7 +4669,7 @@
         <v>49</v>
       </c>
       <c r="J48" s="6">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>36</v>
@@ -4707,7 +4707,7 @@
         <v>55</v>
       </c>
       <c r="J49" s="8">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>36</v>
@@ -4745,7 +4745,7 @@
         <v>35</v>
       </c>
       <c r="J50" s="6">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="K50" s="5" t="s">
         <v>36</v>
@@ -4783,7 +4783,7 @@
         <v>43</v>
       </c>
       <c r="J51" s="8">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>36</v>
@@ -4821,7 +4821,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="6">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>36</v>
@@ -4859,7 +4859,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="8">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>36</v>
@@ -4897,7 +4897,7 @@
         <v>35</v>
       </c>
       <c r="J54" s="6">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>36</v>
@@ -4935,7 +4935,7 @@
         <v>43</v>
       </c>
       <c r="J55" s="8">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>36</v>
@@ -4973,7 +4973,7 @@
         <v>49</v>
       </c>
       <c r="J56" s="6">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>36</v>
@@ -5011,7 +5011,7 @@
         <v>55</v>
       </c>
       <c r="J57" s="8">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>36</v>
@@ -5049,7 +5049,7 @@
         <v>35</v>
       </c>
       <c r="J58" s="6">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>36</v>
@@ -5087,7 +5087,7 @@
         <v>43</v>
       </c>
       <c r="J59" s="8">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>36</v>
@@ -5125,7 +5125,7 @@
         <v>49</v>
       </c>
       <c r="J60" s="6">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>36</v>
@@ -5163,7 +5163,7 @@
         <v>55</v>
       </c>
       <c r="J61" s="8">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>36</v>
@@ -5201,7 +5201,7 @@
         <v>35</v>
       </c>
       <c r="J62" s="6">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>36</v>
@@ -5239,7 +5239,7 @@
         <v>43</v>
       </c>
       <c r="J63" s="8">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>36</v>
@@ -5277,7 +5277,7 @@
         <v>49</v>
       </c>
       <c r="J64" s="6">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="K64" s="5" t="s">
         <v>36</v>
@@ -5315,7 +5315,7 @@
         <v>55</v>
       </c>
       <c r="J65" s="8">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>36</v>
@@ -5353,7 +5353,7 @@
         <v>35</v>
       </c>
       <c r="J66" s="6">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="K66" s="5" t="s">
         <v>36</v>
@@ -5391,7 +5391,7 @@
         <v>43</v>
       </c>
       <c r="J67" s="8">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>36</v>
@@ -5429,7 +5429,7 @@
         <v>49</v>
       </c>
       <c r="J68" s="6">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="K68" s="5" t="s">
         <v>36</v>
@@ -5467,7 +5467,7 @@
         <v>55</v>
       </c>
       <c r="J69" s="8">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="K69" s="9" t="s">
         <v>36</v>
@@ -5505,7 +5505,7 @@
         <v>35</v>
       </c>
       <c r="J70" s="6">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K70" s="5" t="s">
         <v>36</v>
@@ -5543,7 +5543,7 @@
         <v>43</v>
       </c>
       <c r="J71" s="8">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="K71" s="9" t="s">
         <v>36</v>
@@ -5581,7 +5581,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="6">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="K72" s="5" t="s">
         <v>36</v>
@@ -5619,7 +5619,7 @@
         <v>55</v>
       </c>
       <c r="J73" s="8">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K73" s="9" t="s">
         <v>36</v>
@@ -5657,7 +5657,7 @@
         <v>35</v>
       </c>
       <c r="J74" s="6">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K74" s="5" t="s">
         <v>36</v>
@@ -5695,7 +5695,7 @@
         <v>43</v>
       </c>
       <c r="J75" s="8">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>36</v>
@@ -5733,7 +5733,7 @@
         <v>49</v>
       </c>
       <c r="J76" s="6">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="K76" s="5" t="s">
         <v>36</v>
@@ -5771,7 +5771,7 @@
         <v>55</v>
       </c>
       <c r="J77" s="8">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K77" s="9" t="s">
         <v>36</v>
@@ -5809,7 +5809,7 @@
         <v>35</v>
       </c>
       <c r="J78" s="6">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K78" s="5" t="s">
         <v>36</v>
@@ -5847,7 +5847,7 @@
         <v>43</v>
       </c>
       <c r="J79" s="8">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>36</v>
@@ -5885,7 +5885,7 @@
         <v>49</v>
       </c>
       <c r="J80" s="6">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>36</v>
@@ -5923,7 +5923,7 @@
         <v>55</v>
       </c>
       <c r="J81" s="8">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>36</v>
@@ -5961,7 +5961,7 @@
         <v>35</v>
       </c>
       <c r="J82" s="6">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K82" s="5" t="s">
         <v>36</v>
@@ -5999,7 +5999,7 @@
         <v>43</v>
       </c>
       <c r="J83" s="8">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>36</v>
@@ -6037,7 +6037,7 @@
         <v>49</v>
       </c>
       <c r="J84" s="6">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>36</v>
@@ -6075,7 +6075,7 @@
         <v>55</v>
       </c>
       <c r="J85" s="8">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K85" s="9" t="s">
         <v>36</v>
@@ -6113,7 +6113,7 @@
         <v>35</v>
       </c>
       <c r="J86" s="6">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="K86" s="5" t="s">
         <v>36</v>
@@ -6151,7 +6151,7 @@
         <v>43</v>
       </c>
       <c r="J87" s="8">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>36</v>
@@ -6189,7 +6189,7 @@
         <v>49</v>
       </c>
       <c r="J88" s="6">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="K88" s="5" t="s">
         <v>36</v>
@@ -6227,7 +6227,7 @@
         <v>55</v>
       </c>
       <c r="J89" s="8">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="K89" s="9" t="s">
         <v>36</v>
@@ -6265,7 +6265,7 @@
         <v>35</v>
       </c>
       <c r="J90" s="6">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>36</v>
@@ -6303,7 +6303,7 @@
         <v>43</v>
       </c>
       <c r="J91" s="8">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>36</v>
@@ -6341,7 +6341,7 @@
         <v>49</v>
       </c>
       <c r="J92" s="6">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>36</v>
@@ -6379,7 +6379,7 @@
         <v>55</v>
       </c>
       <c r="J93" s="8">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K93" s="9" t="s">
         <v>36</v>
@@ -6417,7 +6417,7 @@
         <v>35</v>
       </c>
       <c r="J94" s="6">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="K94" s="5" t="s">
         <v>36</v>
@@ -6455,7 +6455,7 @@
         <v>43</v>
       </c>
       <c r="J95" s="8">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="K95" s="9" t="s">
         <v>36</v>
@@ -6493,7 +6493,7 @@
         <v>49</v>
       </c>
       <c r="J96" s="6">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K96" s="5" t="s">
         <v>36</v>
@@ -6531,7 +6531,7 @@
         <v>55</v>
       </c>
       <c r="J97" s="8">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K97" s="9" t="s">
         <v>36</v>
@@ -6569,7 +6569,7 @@
         <v>35</v>
       </c>
       <c r="J98" s="6">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="K98" s="5" t="s">
         <v>36</v>
@@ -6607,7 +6607,7 @@
         <v>43</v>
       </c>
       <c r="J99" s="8">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="K99" s="9" t="s">
         <v>36</v>
@@ -6645,7 +6645,7 @@
         <v>49</v>
       </c>
       <c r="J100" s="6">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="K100" s="5" t="s">
         <v>36</v>
@@ -6683,7 +6683,7 @@
         <v>55</v>
       </c>
       <c r="J101" s="8">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K101" s="9" t="s">
         <v>36</v>
@@ -6721,7 +6721,7 @@
         <v>35</v>
       </c>
       <c r="J102" s="6">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="K102" s="5" t="s">
         <v>36</v>
@@ -6759,7 +6759,7 @@
         <v>43</v>
       </c>
       <c r="J103" s="8">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="K103" s="9" t="s">
         <v>36</v>
@@ -6797,7 +6797,7 @@
         <v>49</v>
       </c>
       <c r="J104" s="6">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="K104" s="5" t="s">
         <v>36</v>
@@ -6835,7 +6835,7 @@
         <v>55</v>
       </c>
       <c r="J105" s="8">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K105" s="9" t="s">
         <v>36</v>
@@ -6873,7 +6873,7 @@
         <v>35</v>
       </c>
       <c r="J106" s="6">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="K106" s="5" t="s">
         <v>36</v>
@@ -6911,7 +6911,7 @@
         <v>43</v>
       </c>
       <c r="J107" s="8">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="K107" s="9" t="s">
         <v>36</v>
@@ -6949,7 +6949,7 @@
         <v>49</v>
       </c>
       <c r="J108" s="6">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="K108" s="5" t="s">
         <v>36</v>
@@ -6987,7 +6987,7 @@
         <v>55</v>
       </c>
       <c r="J109" s="8">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K109" s="9" t="s">
         <v>36</v>
@@ -7025,7 +7025,7 @@
         <v>35</v>
       </c>
       <c r="J110" s="6">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="K110" s="5" t="s">
         <v>36</v>
@@ -7063,7 +7063,7 @@
         <v>43</v>
       </c>
       <c r="J111" s="8">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K111" s="9" t="s">
         <v>36</v>
@@ -7101,7 +7101,7 @@
         <v>49</v>
       </c>
       <c r="J112" s="6">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>36</v>
@@ -7139,7 +7139,7 @@
         <v>55</v>
       </c>
       <c r="J113" s="8">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>36</v>
@@ -7177,7 +7177,7 @@
         <v>35</v>
       </c>
       <c r="J114" s="6">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="K114" s="5" t="s">
         <v>36</v>
@@ -7215,7 +7215,7 @@
         <v>43</v>
       </c>
       <c r="J115" s="8">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="K115" s="9" t="s">
         <v>36</v>
@@ -7253,7 +7253,7 @@
         <v>49</v>
       </c>
       <c r="J116" s="6">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="K116" s="5" t="s">
         <v>36</v>
@@ -7291,7 +7291,7 @@
         <v>55</v>
       </c>
       <c r="J117" s="8">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="K117" s="9" t="s">
         <v>36</v>
@@ -7329,7 +7329,7 @@
         <v>35</v>
       </c>
       <c r="J118" s="6">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="K118" s="5" t="s">
         <v>36</v>
@@ -7367,7 +7367,7 @@
         <v>43</v>
       </c>
       <c r="J119" s="8">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="K119" s="9" t="s">
         <v>36</v>
@@ -7405,7 +7405,7 @@
         <v>49</v>
       </c>
       <c r="J120" s="6">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="K120" s="5" t="s">
         <v>36</v>
@@ -7443,7 +7443,7 @@
         <v>55</v>
       </c>
       <c r="J121" s="8">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="K121" s="9" t="s">
         <v>36</v>
@@ -7481,7 +7481,7 @@
         <v>35</v>
       </c>
       <c r="J122" s="6">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="K122" s="5" t="s">
         <v>36</v>
@@ -7519,7 +7519,7 @@
         <v>43</v>
       </c>
       <c r="J123" s="8">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="K123" s="9" t="s">
         <v>36</v>
@@ -7557,7 +7557,7 @@
         <v>49</v>
       </c>
       <c r="J124" s="6">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="K124" s="5" t="s">
         <v>36</v>
@@ -7595,7 +7595,7 @@
         <v>55</v>
       </c>
       <c r="J125" s="8">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="K125" s="9" t="s">
         <v>36</v>
@@ -7633,7 +7633,7 @@
         <v>35</v>
       </c>
       <c r="J126" s="6">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="K126" s="5" t="s">
         <v>36</v>
@@ -7671,7 +7671,7 @@
         <v>43</v>
       </c>
       <c r="J127" s="8">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="K127" s="9" t="s">
         <v>36</v>
@@ -7709,7 +7709,7 @@
         <v>49</v>
       </c>
       <c r="J128" s="6">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="K128" s="5" t="s">
         <v>36</v>
@@ -7747,7 +7747,7 @@
         <v>55</v>
       </c>
       <c r="J129" s="8">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="K129" s="9" t="s">
         <v>36</v>
@@ -7785,7 +7785,7 @@
         <v>35</v>
       </c>
       <c r="J130" s="6">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K130" s="5" t="s">
         <v>36</v>
@@ -7823,7 +7823,7 @@
         <v>43</v>
       </c>
       <c r="J131" s="8">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="K131" s="9" t="s">
         <v>36</v>
@@ -7861,7 +7861,7 @@
         <v>49</v>
       </c>
       <c r="J132" s="6">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="K132" s="5" t="s">
         <v>36</v>
@@ -7899,7 +7899,7 @@
         <v>55</v>
       </c>
       <c r="J133" s="8">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="K133" s="9" t="s">
         <v>36</v>
@@ -7937,7 +7937,7 @@
         <v>35</v>
       </c>
       <c r="J134" s="6">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="K134" s="5" t="s">
         <v>36</v>
@@ -7975,7 +7975,7 @@
         <v>43</v>
       </c>
       <c r="J135" s="8">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K135" s="9" t="s">
         <v>36</v>
@@ -8013,7 +8013,7 @@
         <v>49</v>
       </c>
       <c r="J136" s="6">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="K136" s="5" t="s">
         <v>36</v>
@@ -8051,7 +8051,7 @@
         <v>55</v>
       </c>
       <c r="J137" s="8">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K137" s="9" t="s">
         <v>36</v>
@@ -8089,7 +8089,7 @@
         <v>35</v>
       </c>
       <c r="J138" s="6">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="K138" s="5" t="s">
         <v>36</v>
@@ -8127,7 +8127,7 @@
         <v>43</v>
       </c>
       <c r="J139" s="8">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="K139" s="9" t="s">
         <v>36</v>
@@ -8165,7 +8165,7 @@
         <v>49</v>
       </c>
       <c r="J140" s="6">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="K140" s="5" t="s">
         <v>36</v>
@@ -8203,7 +8203,7 @@
         <v>55</v>
       </c>
       <c r="J141" s="8">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="K141" s="9" t="s">
         <v>36</v>
@@ -8241,7 +8241,7 @@
         <v>35</v>
       </c>
       <c r="J142" s="6">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="K142" s="5" t="s">
         <v>36</v>
@@ -8279,7 +8279,7 @@
         <v>43</v>
       </c>
       <c r="J143" s="8">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="K143" s="9" t="s">
         <v>36</v>
@@ -8317,7 +8317,7 @@
         <v>49</v>
       </c>
       <c r="J144" s="6">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="K144" s="5" t="s">
         <v>36</v>
@@ -8355,7 +8355,7 @@
         <v>55</v>
       </c>
       <c r="J145" s="8">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="K145" s="9" t="s">
         <v>36</v>
@@ -8393,7 +8393,7 @@
         <v>35</v>
       </c>
       <c r="J146" s="6">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K146" s="5" t="s">
         <v>36</v>
@@ -8431,7 +8431,7 @@
         <v>43</v>
       </c>
       <c r="J147" s="8">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="K147" s="9" t="s">
         <v>36</v>
@@ -8469,7 +8469,7 @@
         <v>49</v>
       </c>
       <c r="J148" s="6">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="K148" s="5" t="s">
         <v>36</v>
@@ -8507,7 +8507,7 @@
         <v>55</v>
       </c>
       <c r="J149" s="8">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="K149" s="9" t="s">
         <v>36</v>
@@ -8545,7 +8545,7 @@
         <v>35</v>
       </c>
       <c r="J150" s="6">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="K150" s="5" t="s">
         <v>36</v>
@@ -8583,7 +8583,7 @@
         <v>43</v>
       </c>
       <c r="J151" s="8">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K151" s="9" t="s">
         <v>36</v>
@@ -8621,7 +8621,7 @@
         <v>49</v>
       </c>
       <c r="J152" s="6">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>36</v>
@@ -8659,7 +8659,7 @@
         <v>55</v>
       </c>
       <c r="J153" s="8">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="K153" s="9" t="s">
         <v>36</v>
@@ -8697,7 +8697,7 @@
         <v>35</v>
       </c>
       <c r="J154" s="6">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="K154" s="5" t="s">
         <v>36</v>
@@ -8735,7 +8735,7 @@
         <v>43</v>
       </c>
       <c r="J155" s="8">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="K155" s="9" t="s">
         <v>36</v>
@@ -8773,7 +8773,7 @@
         <v>49</v>
       </c>
       <c r="J156" s="6">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="K156" s="5" t="s">
         <v>36</v>
@@ -8811,7 +8811,7 @@
         <v>55</v>
       </c>
       <c r="J157" s="8">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="K157" s="9" t="s">
         <v>36</v>
@@ -8849,7 +8849,7 @@
         <v>35</v>
       </c>
       <c r="J158" s="6">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="K158" s="5" t="s">
         <v>36</v>
@@ -8887,7 +8887,7 @@
         <v>43</v>
       </c>
       <c r="J159" s="8">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="K159" s="9" t="s">
         <v>36</v>
@@ -8925,7 +8925,7 @@
         <v>49</v>
       </c>
       <c r="J160" s="6">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="K160" s="5" t="s">
         <v>36</v>
@@ -8963,7 +8963,7 @@
         <v>55</v>
       </c>
       <c r="J161" s="8">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="K161" s="9" t="s">
         <v>36</v>
@@ -9001,7 +9001,7 @@
         <v>35</v>
       </c>
       <c r="J162" s="6">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="K162" s="5" t="s">
         <v>36</v>
@@ -9039,7 +9039,7 @@
         <v>43</v>
       </c>
       <c r="J163" s="8">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="K163" s="9" t="s">
         <v>36</v>
@@ -9077,7 +9077,7 @@
         <v>49</v>
       </c>
       <c r="J164" s="6">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K164" s="5" t="s">
         <v>36</v>
@@ -9115,7 +9115,7 @@
         <v>55</v>
       </c>
       <c r="J165" s="8">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K165" s="9" t="s">
         <v>36</v>
@@ -9153,7 +9153,7 @@
         <v>35</v>
       </c>
       <c r="J166" s="6">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>36</v>
@@ -9191,7 +9191,7 @@
         <v>43</v>
       </c>
       <c r="J167" s="8">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="K167" s="9" t="s">
         <v>36</v>
@@ -9229,7 +9229,7 @@
         <v>49</v>
       </c>
       <c r="J168" s="6">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="K168" s="5" t="s">
         <v>36</v>
@@ -9267,7 +9267,7 @@
         <v>55</v>
       </c>
       <c r="J169" s="8">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K169" s="9" t="s">
         <v>36</v>
@@ -9305,7 +9305,7 @@
         <v>35</v>
       </c>
       <c r="J170" s="6">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="K170" s="5" t="s">
         <v>36</v>
@@ -9343,7 +9343,7 @@
         <v>43</v>
       </c>
       <c r="J171" s="8">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="K171" s="9" t="s">
         <v>36</v>
@@ -9381,7 +9381,7 @@
         <v>49</v>
       </c>
       <c r="J172" s="6">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="K172" s="5" t="s">
         <v>36</v>
@@ -9419,7 +9419,7 @@
         <v>55</v>
       </c>
       <c r="J173" s="8">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="K173" s="9" t="s">
         <v>36</v>
@@ -9457,7 +9457,7 @@
         <v>35</v>
       </c>
       <c r="J174" s="6">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K174" s="5" t="s">
         <v>36</v>
@@ -9495,7 +9495,7 @@
         <v>43</v>
       </c>
       <c r="J175" s="8">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="K175" s="9" t="s">
         <v>36</v>
@@ -9533,7 +9533,7 @@
         <v>49</v>
       </c>
       <c r="J176" s="6">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="K176" s="5" t="s">
         <v>36</v>
@@ -9571,7 +9571,7 @@
         <v>55</v>
       </c>
       <c r="J177" s="8">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="K177" s="9" t="s">
         <v>36</v>
@@ -9609,7 +9609,7 @@
         <v>35</v>
       </c>
       <c r="J178" s="6">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="K178" s="5" t="s">
         <v>36</v>
@@ -9647,7 +9647,7 @@
         <v>43</v>
       </c>
       <c r="J179" s="8">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="K179" s="9" t="s">
         <v>36</v>
@@ -9685,7 +9685,7 @@
         <v>49</v>
       </c>
       <c r="J180" s="6">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="K180" s="5" t="s">
         <v>36</v>
@@ -9723,7 +9723,7 @@
         <v>55</v>
       </c>
       <c r="J181" s="8">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="K181" s="9" t="s">
         <v>36</v>
@@ -9761,7 +9761,7 @@
         <v>35</v>
       </c>
       <c r="J182" s="6">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="K182" s="5" t="s">
         <v>36</v>
@@ -9799,7 +9799,7 @@
         <v>43</v>
       </c>
       <c r="J183" s="8">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="K183" s="9" t="s">
         <v>36</v>
@@ -9837,7 +9837,7 @@
         <v>49</v>
       </c>
       <c r="J184" s="6">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="K184" s="5" t="s">
         <v>36</v>
@@ -9875,7 +9875,7 @@
         <v>55</v>
       </c>
       <c r="J185" s="8">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="K185" s="9" t="s">
         <v>36</v>
@@ -9913,7 +9913,7 @@
         <v>35</v>
       </c>
       <c r="J186" s="6">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="K186" s="5" t="s">
         <v>36</v>
@@ -9951,7 +9951,7 @@
         <v>43</v>
       </c>
       <c r="J187" s="8">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>36</v>
@@ -9989,7 +9989,7 @@
         <v>49</v>
       </c>
       <c r="J188" s="6">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="K188" s="5" t="s">
         <v>36</v>
@@ -10027,7 +10027,7 @@
         <v>55</v>
       </c>
       <c r="J189" s="8">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>36</v>
@@ -10065,7 +10065,7 @@
         <v>35</v>
       </c>
       <c r="J190" s="6">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="K190" s="5" t="s">
         <v>36</v>
@@ -10103,7 +10103,7 @@
         <v>43</v>
       </c>
       <c r="J191" s="8">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>36</v>
@@ -10141,7 +10141,7 @@
         <v>49</v>
       </c>
       <c r="J192" s="6">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="K192" s="5" t="s">
         <v>36</v>
@@ -10179,7 +10179,7 @@
         <v>55</v>
       </c>
       <c r="J193" s="8">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>36</v>
@@ -10217,7 +10217,7 @@
         <v>35</v>
       </c>
       <c r="J194" s="6">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="K194" s="5" t="s">
         <v>36</v>
@@ -10255,7 +10255,7 @@
         <v>43</v>
       </c>
       <c r="J195" s="8">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>36</v>
@@ -10293,7 +10293,7 @@
         <v>49</v>
       </c>
       <c r="J196" s="6">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="K196" s="5" t="s">
         <v>36</v>
@@ -10331,7 +10331,7 @@
         <v>55</v>
       </c>
       <c r="J197" s="8">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K197" s="9" t="s">
         <v>36</v>
@@ -10369,7 +10369,7 @@
         <v>35</v>
       </c>
       <c r="J198" s="6">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K198" s="5" t="s">
         <v>36</v>
@@ -10407,7 +10407,7 @@
         <v>43</v>
       </c>
       <c r="J199" s="8">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="K199" s="9" t="s">
         <v>36</v>
@@ -10445,7 +10445,7 @@
         <v>49</v>
       </c>
       <c r="J200" s="6">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="K200" s="5" t="s">
         <v>36</v>
@@ -10483,7 +10483,7 @@
         <v>55</v>
       </c>
       <c r="J201" s="8">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="K201" s="9" t="s">
         <v>36</v>
@@ -10521,7 +10521,7 @@
         <v>35</v>
       </c>
       <c r="J202" s="6">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="K202" s="5" t="s">
         <v>36</v>
@@ -10559,7 +10559,7 @@
         <v>43</v>
       </c>
       <c r="J203" s="8">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K203" s="9" t="s">
         <v>36</v>
@@ -10597,7 +10597,7 @@
         <v>49</v>
       </c>
       <c r="J204" s="6">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="K204" s="5" t="s">
         <v>36</v>
@@ -10635,7 +10635,7 @@
         <v>55</v>
       </c>
       <c r="J205" s="8">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="K205" s="9" t="s">
         <v>36</v>
@@ -10673,7 +10673,7 @@
         <v>35</v>
       </c>
       <c r="J206" s="6">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="K206" s="5" t="s">
         <v>36</v>
@@ -10711,7 +10711,7 @@
         <v>43</v>
       </c>
       <c r="J207" s="8">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="K207" s="9" t="s">
         <v>36</v>
@@ -10749,7 +10749,7 @@
         <v>49</v>
       </c>
       <c r="J208" s="6">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="K208" s="5" t="s">
         <v>36</v>
@@ -10787,7 +10787,7 @@
         <v>55</v>
       </c>
       <c r="J209" s="8">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="K209" s="9" t="s">
         <v>36</v>
@@ -10825,7 +10825,7 @@
         <v>35</v>
       </c>
       <c r="J210" s="6">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="K210" s="5" t="s">
         <v>36</v>
@@ -10863,7 +10863,7 @@
         <v>43</v>
       </c>
       <c r="J211" s="8">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>36</v>
@@ -10901,7 +10901,7 @@
         <v>49</v>
       </c>
       <c r="J212" s="6">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="K212" s="5" t="s">
         <v>36</v>
@@ -10939,7 +10939,7 @@
         <v>55</v>
       </c>
       <c r="J213" s="8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K213" s="9" t="s">
         <v>36</v>
@@ -10977,7 +10977,7 @@
         <v>35</v>
       </c>
       <c r="J214" s="6">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="K214" s="5" t="s">
         <v>36</v>
@@ -11015,7 +11015,7 @@
         <v>43</v>
       </c>
       <c r="J215" s="8">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="K215" s="9" t="s">
         <v>36</v>
@@ -11053,7 +11053,7 @@
         <v>49</v>
       </c>
       <c r="J216" s="6">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="K216" s="5" t="s">
         <v>36</v>
@@ -11091,7 +11091,7 @@
         <v>55</v>
       </c>
       <c r="J217" s="8">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K217" s="9" t="s">
         <v>36</v>
@@ -11129,7 +11129,7 @@
         <v>35</v>
       </c>
       <c r="J218" s="6">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="K218" s="5" t="s">
         <v>36</v>
@@ -11167,7 +11167,7 @@
         <v>43</v>
       </c>
       <c r="J219" s="8">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K219" s="9" t="s">
         <v>36</v>
@@ -11205,7 +11205,7 @@
         <v>49</v>
       </c>
       <c r="J220" s="6">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="K220" s="5" t="s">
         <v>36</v>
@@ -11243,7 +11243,7 @@
         <v>55</v>
       </c>
       <c r="J221" s="8">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="K221" s="9" t="s">
         <v>36</v>
@@ -11281,7 +11281,7 @@
         <v>35</v>
       </c>
       <c r="J222" s="6">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="K222" s="5" t="s">
         <v>36</v>
@@ -11319,7 +11319,7 @@
         <v>43</v>
       </c>
       <c r="J223" s="8">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K223" s="9" t="s">
         <v>36</v>
@@ -11357,7 +11357,7 @@
         <v>49</v>
       </c>
       <c r="J224" s="6">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="K224" s="5" t="s">
         <v>36</v>
@@ -11395,7 +11395,7 @@
         <v>55</v>
       </c>
       <c r="J225" s="8">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K225" s="9" t="s">
         <v>36</v>
@@ -11433,7 +11433,7 @@
         <v>35</v>
       </c>
       <c r="J226" s="6">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="K226" s="5" t="s">
         <v>36</v>
@@ -11471,7 +11471,7 @@
         <v>43</v>
       </c>
       <c r="J227" s="8">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K227" s="9" t="s">
         <v>36</v>
@@ -11509,7 +11509,7 @@
         <v>49</v>
       </c>
       <c r="J228" s="6">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="K228" s="5" t="s">
         <v>36</v>
@@ -11547,7 +11547,7 @@
         <v>55</v>
       </c>
       <c r="J229" s="8">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="K229" s="9" t="s">
         <v>36</v>
@@ -11585,7 +11585,7 @@
         <v>35</v>
       </c>
       <c r="J230" s="6">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="K230" s="5" t="s">
         <v>36</v>
@@ -11623,7 +11623,7 @@
         <v>43</v>
       </c>
       <c r="J231" s="8">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="K231" s="9" t="s">
         <v>36</v>
@@ -11661,7 +11661,7 @@
         <v>49</v>
       </c>
       <c r="J232" s="6">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="K232" s="5" t="s">
         <v>36</v>
@@ -11699,7 +11699,7 @@
         <v>55</v>
       </c>
       <c r="J233" s="8">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="K233" s="9" t="s">
         <v>36</v>
@@ -11737,7 +11737,7 @@
         <v>35</v>
       </c>
       <c r="J234" s="6">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="K234" s="5" t="s">
         <v>36</v>
@@ -11775,7 +11775,7 @@
         <v>43</v>
       </c>
       <c r="J235" s="8">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="K235" s="9" t="s">
         <v>36</v>
@@ -11813,7 +11813,7 @@
         <v>49</v>
       </c>
       <c r="J236" s="6">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="K236" s="5" t="s">
         <v>36</v>
@@ -11851,7 +11851,7 @@
         <v>55</v>
       </c>
       <c r="J237" s="8">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="K237" s="9" t="s">
         <v>36</v>
@@ -11889,7 +11889,7 @@
         <v>35</v>
       </c>
       <c r="J238" s="6">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="K238" s="5" t="s">
         <v>36</v>
@@ -11927,7 +11927,7 @@
         <v>43</v>
       </c>
       <c r="J239" s="8">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="K239" s="9" t="s">
         <v>36</v>
@@ -11965,7 +11965,7 @@
         <v>49</v>
       </c>
       <c r="J240" s="6">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K240" s="5" t="s">
         <v>36</v>
@@ -12003,7 +12003,7 @@
         <v>55</v>
       </c>
       <c r="J241" s="8">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="K241" s="9" t="s">
         <v>36</v>
@@ -12041,7 +12041,7 @@
         <v>35</v>
       </c>
       <c r="J242" s="6">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="K242" s="5" t="s">
         <v>36</v>
@@ -12079,7 +12079,7 @@
         <v>43</v>
       </c>
       <c r="J243" s="8">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="K243" s="9" t="s">
         <v>36</v>
@@ -12117,7 +12117,7 @@
         <v>49</v>
       </c>
       <c r="J244" s="6">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="K244" s="5" t="s">
         <v>36</v>
@@ -12155,7 +12155,7 @@
         <v>55</v>
       </c>
       <c r="J245" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K245" s="9" t="s">
         <v>36</v>
@@ -12193,7 +12193,7 @@
         <v>35</v>
       </c>
       <c r="J246" s="6">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="K246" s="5" t="s">
         <v>36</v>
@@ -12231,7 +12231,7 @@
         <v>43</v>
       </c>
       <c r="J247" s="8">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="K247" s="9" t="s">
         <v>36</v>
@@ -12269,7 +12269,7 @@
         <v>49</v>
       </c>
       <c r="J248" s="6">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K248" s="5" t="s">
         <v>36</v>
@@ -12307,7 +12307,7 @@
         <v>55</v>
       </c>
       <c r="J249" s="8">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="K249" s="9" t="s">
         <v>36</v>
@@ -12345,7 +12345,7 @@
         <v>35</v>
       </c>
       <c r="J250" s="6">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="K250" s="5" t="s">
         <v>36</v>
@@ -12383,7 +12383,7 @@
         <v>43</v>
       </c>
       <c r="J251" s="8">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="K251" s="9" t="s">
         <v>36</v>
@@ -12421,7 +12421,7 @@
         <v>49</v>
       </c>
       <c r="J252" s="6">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K252" s="5" t="s">
         <v>36</v>
@@ -12459,7 +12459,7 @@
         <v>55</v>
       </c>
       <c r="J253" s="8">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K253" s="9" t="s">
         <v>36</v>
@@ -12497,7 +12497,7 @@
         <v>35</v>
       </c>
       <c r="J254" s="6">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K254" s="5" t="s">
         <v>36</v>
@@ -12535,7 +12535,7 @@
         <v>43</v>
       </c>
       <c r="J255" s="8">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="K255" s="9" t="s">
         <v>36</v>
@@ -12573,7 +12573,7 @@
         <v>49</v>
       </c>
       <c r="J256" s="6">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K256" s="5" t="s">
         <v>36</v>
@@ -12611,7 +12611,7 @@
         <v>55</v>
       </c>
       <c r="J257" s="8">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="K257" s="9" t="s">
         <v>36</v>
@@ -12649,7 +12649,7 @@
         <v>35</v>
       </c>
       <c r="J258" s="6">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K258" s="5" t="s">
         <v>36</v>
@@ -12687,7 +12687,7 @@
         <v>43</v>
       </c>
       <c r="J259" s="8">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K259" s="9" t="s">
         <v>36</v>
@@ -12725,7 +12725,7 @@
         <v>49</v>
       </c>
       <c r="J260" s="6">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="K260" s="5" t="s">
         <v>36</v>
@@ -12763,7 +12763,7 @@
         <v>55</v>
       </c>
       <c r="J261" s="8">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="K261" s="9" t="s">
         <v>36</v>
@@ -12801,7 +12801,7 @@
         <v>35</v>
       </c>
       <c r="J262" s="6">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K262" s="5" t="s">
         <v>36</v>
@@ -12839,7 +12839,7 @@
         <v>43</v>
       </c>
       <c r="J263" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K263" s="9" t="s">
         <v>36</v>
@@ -12877,7 +12877,7 @@
         <v>49</v>
       </c>
       <c r="J264" s="6">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="K264" s="5" t="s">
         <v>36</v>
@@ -12915,7 +12915,7 @@
         <v>55</v>
       </c>
       <c r="J265" s="8">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="K265" s="9" t="s">
         <v>36</v>
@@ -12953,7 +12953,7 @@
         <v>35</v>
       </c>
       <c r="J266" s="6">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="K266" s="5" t="s">
         <v>36</v>
@@ -12991,7 +12991,7 @@
         <v>43</v>
       </c>
       <c r="J267" s="8">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="K267" s="9" t="s">
         <v>36</v>
@@ -13029,7 +13029,7 @@
         <v>49</v>
       </c>
       <c r="J268" s="6">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="K268" s="5" t="s">
         <v>36</v>
@@ -13067,7 +13067,7 @@
         <v>55</v>
       </c>
       <c r="J269" s="8">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K269" s="9" t="s">
         <v>36</v>
@@ -13105,7 +13105,7 @@
         <v>35</v>
       </c>
       <c r="J270" s="6">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K270" s="5" t="s">
         <v>36</v>
@@ -13143,7 +13143,7 @@
         <v>43</v>
       </c>
       <c r="J271" s="8">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="K271" s="9" t="s">
         <v>36</v>
@@ -13181,7 +13181,7 @@
         <v>49</v>
       </c>
       <c r="J272" s="6">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="K272" s="5" t="s">
         <v>36</v>
@@ -13219,7 +13219,7 @@
         <v>55</v>
       </c>
       <c r="J273" s="8">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="K273" s="9" t="s">
         <v>36</v>
@@ -13257,7 +13257,7 @@
         <v>35</v>
       </c>
       <c r="J274" s="6">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="K274" s="5" t="s">
         <v>36</v>
@@ -13295,7 +13295,7 @@
         <v>43</v>
       </c>
       <c r="J275" s="8">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="K275" s="9" t="s">
         <v>36</v>
@@ -13333,7 +13333,7 @@
         <v>49</v>
       </c>
       <c r="J276" s="6">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="K276" s="5" t="s">
         <v>36</v>
@@ -13371,7 +13371,7 @@
         <v>55</v>
       </c>
       <c r="J277" s="8">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K277" s="9" t="s">
         <v>36</v>
@@ -13409,7 +13409,7 @@
         <v>35</v>
       </c>
       <c r="J278" s="6">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="K278" s="5" t="s">
         <v>36</v>
@@ -13447,7 +13447,7 @@
         <v>43</v>
       </c>
       <c r="J279" s="8">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="K279" s="9" t="s">
         <v>36</v>
@@ -13485,7 +13485,7 @@
         <v>49</v>
       </c>
       <c r="J280" s="6">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="K280" s="5" t="s">
         <v>36</v>
@@ -13523,7 +13523,7 @@
         <v>55</v>
       </c>
       <c r="J281" s="8">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="K281" s="9" t="s">
         <v>36</v>
@@ -13561,7 +13561,7 @@
         <v>35</v>
       </c>
       <c r="J282" s="6">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="K282" s="5" t="s">
         <v>36</v>
@@ -13599,7 +13599,7 @@
         <v>43</v>
       </c>
       <c r="J283" s="8">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="K283" s="9" t="s">
         <v>36</v>
@@ -13637,7 +13637,7 @@
         <v>49</v>
       </c>
       <c r="J284" s="6">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="K284" s="5" t="s">
         <v>36</v>
@@ -13675,7 +13675,7 @@
         <v>55</v>
       </c>
       <c r="J285" s="8">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="K285" s="9" t="s">
         <v>36</v>
@@ -13713,7 +13713,7 @@
         <v>35</v>
       </c>
       <c r="J286" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K286" s="5" t="s">
         <v>36</v>
@@ -13751,7 +13751,7 @@
         <v>43</v>
       </c>
       <c r="J287" s="8">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="K287" s="9" t="s">
         <v>36</v>
@@ -13789,7 +13789,7 @@
         <v>49</v>
       </c>
       <c r="J288" s="6">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="K288" s="5" t="s">
         <v>36</v>
@@ -13827,7 +13827,7 @@
         <v>55</v>
       </c>
       <c r="J289" s="8">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="K289" s="9" t="s">
         <v>36</v>
@@ -13865,7 +13865,7 @@
         <v>35</v>
       </c>
       <c r="J290" s="6">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="K290" s="5" t="s">
         <v>36</v>
@@ -13903,7 +13903,7 @@
         <v>43</v>
       </c>
       <c r="J291" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K291" s="9" t="s">
         <v>36</v>
@@ -13941,7 +13941,7 @@
         <v>49</v>
       </c>
       <c r="J292" s="6">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K292" s="5" t="s">
         <v>36</v>
@@ -13979,7 +13979,7 @@
         <v>55</v>
       </c>
       <c r="J293" s="8">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="K293" s="9" t="s">
         <v>36</v>
@@ -14017,7 +14017,7 @@
         <v>35</v>
       </c>
       <c r="J294" s="6">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="K294" s="5" t="s">
         <v>36</v>
@@ -14055,7 +14055,7 @@
         <v>43</v>
       </c>
       <c r="J295" s="8">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="K295" s="9" t="s">
         <v>36</v>
@@ -14131,7 +14131,7 @@
         <v>55</v>
       </c>
       <c r="J297" s="8">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="K297" s="9" t="s">
         <v>36</v>
@@ -14169,7 +14169,7 @@
         <v>35</v>
       </c>
       <c r="J298" s="6">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="K298" s="5" t="s">
         <v>36</v>
@@ -14207,7 +14207,7 @@
         <v>43</v>
       </c>
       <c r="J299" s="8">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K299" s="9" t="s">
         <v>36</v>
@@ -14245,7 +14245,7 @@
         <v>49</v>
       </c>
       <c r="J300" s="6">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="K300" s="5" t="s">
         <v>36</v>
@@ -14283,7 +14283,7 @@
         <v>55</v>
       </c>
       <c r="J301" s="8">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="K301" s="9" t="s">
         <v>36</v>
